--- a/grade_workbook_plus_calculater.xlsx
+++ b/grade_workbook_plus_calculater.xlsx
@@ -8,20 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/1004953/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA2F3ED-883D-DB47-81C8-EB630D882AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{736E6BB0-B4CA-8343-88F1-FDB0F3581FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="4" xr2:uid="{14F85899-1210-B148-8CD6-CA12EBDA61AB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{14F85899-1210-B148-8CD6-CA12EBDA61AB}"/>
   </bookViews>
   <sheets>
     <sheet name="grade_table" sheetId="2" r:id="rId1"/>
-    <sheet name="Q1" sheetId="11" r:id="rId2"/>
-    <sheet name="Q2" sheetId="12" r:id="rId3"/>
-    <sheet name="Q3" sheetId="13" r:id="rId4"/>
-    <sheet name="Q4" sheetId="9" r:id="rId5"/>
-    <sheet name="qp_table" sheetId="3" r:id="rId6"/>
-    <sheet name="quarter_grades" sheetId="4" r:id="rId7"/>
-    <sheet name="Your_QP_table" sheetId="5" r:id="rId8"/>
+    <sheet name="Scenario Summary 4" sheetId="18" r:id="rId2"/>
+    <sheet name="Sheet9" sheetId="19" r:id="rId3"/>
+    <sheet name="Q1" sheetId="11" r:id="rId4"/>
+    <sheet name="Q2" sheetId="12" r:id="rId5"/>
+    <sheet name="Q3" sheetId="13" r:id="rId6"/>
+    <sheet name="Q4" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="14" r:id="rId8"/>
+    <sheet name="qp_table" sheetId="3" r:id="rId9"/>
+    <sheet name="quarter_grades" sheetId="4" r:id="rId10"/>
+    <sheet name="Your_QP_table" sheetId="5" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="Calculues_1_summary" localSheetId="3">Sheet4!$J$1:$N$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="88">
   <si>
     <t>Low</t>
   </si>
@@ -165,17 +171,162 @@
     <t>Points Earned</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
     <t>9000%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90.00 </t>
+  </si>
+  <si>
+    <t>$K$3</t>
+  </si>
+  <si>
+    <t>$L$3</t>
+  </si>
+  <si>
+    <t>$M$3</t>
+  </si>
+  <si>
+    <t>Scenario Summary</t>
+  </si>
+  <si>
+    <t>Changing Cells:</t>
+  </si>
+  <si>
+    <t>Current Values:</t>
+  </si>
+  <si>
+    <t>Notes:  Current Values column represents values of changing cells at</t>
+  </si>
+  <si>
+    <t>time Scenario Summary Report was created.  Changing cells for each</t>
+  </si>
+  <si>
+    <t>scenario are highlighted in gray.</t>
+  </si>
+  <si>
+    <t>$F$3</t>
+  </si>
+  <si>
+    <t>$G$3</t>
+  </si>
+  <si>
+    <t>$H$3</t>
+  </si>
+  <si>
+    <t>$F$4</t>
+  </si>
+  <si>
+    <t>$G$4</t>
+  </si>
+  <si>
+    <t>$H$4</t>
+  </si>
+  <si>
+    <t>$F$5</t>
+  </si>
+  <si>
+    <t>$G$5</t>
+  </si>
+  <si>
+    <t>$H$5</t>
+  </si>
+  <si>
+    <t>$F$6</t>
+  </si>
+  <si>
+    <t>$G$6</t>
+  </si>
+  <si>
+    <t>$H$6</t>
+  </si>
+  <si>
+    <t>$F$7</t>
+  </si>
+  <si>
+    <t>$G$7</t>
+  </si>
+  <si>
+    <t>$H$7</t>
+  </si>
+  <si>
+    <t>$F$8</t>
+  </si>
+  <si>
+    <t>$G$8</t>
+  </si>
+  <si>
+    <t>$H$8</t>
+  </si>
+  <si>
+    <t>$B$2</t>
+  </si>
+  <si>
+    <t>$C$2</t>
+  </si>
+  <si>
+    <t>$B$3</t>
+  </si>
+  <si>
+    <t>$C$3</t>
+  </si>
+  <si>
+    <t>$B$4</t>
+  </si>
+  <si>
+    <t>$C$4</t>
+  </si>
+  <si>
+    <t>$B$5</t>
+  </si>
+  <si>
+    <t>$C$5</t>
+  </si>
+  <si>
+    <t>$B$6</t>
+  </si>
+  <si>
+    <t>$C$6</t>
+  </si>
+  <si>
+    <t>$B$7</t>
+  </si>
+  <si>
+    <t>$C$7</t>
+  </si>
+  <si>
+    <t>$B$8</t>
+  </si>
+  <si>
+    <t>$C$8</t>
+  </si>
+  <si>
+    <t>$B$9</t>
+  </si>
+  <si>
+    <t>$C$9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1 final </t>
+  </si>
+  <si>
+    <t>Created by Arnez, Paul on 10/1/2026
+Modified by Arnez, Paul on 10/1/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -211,8 +362,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color indexed="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="18"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -243,8 +431,26 @@
         <bgColor rgb="FF196B24"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -360,12 +566,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -380,11 +607,45 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
@@ -521,6 +782,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{688193E8-BF00-EC5F-CF15-E8BF060B6006}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="482600" y="114300"/>
+          <a:ext cx="7772400" cy="4180609"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -572,7 +882,7 @@
   <autoFilter ref="E2:H3" xr:uid="{21625636-6A1F-7641-BEAA-29566C95DBEE}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5265991A-0CB6-BA4B-BD4A-27FB9F24DDFC}" name="Assignment Name"/>
-    <tableColumn id="2" xr3:uid="{837B4DEA-431B-8140-90EC-AF1426BB3C6B}" name="Grade you got" totalsRowLabel="9000%" totalsRowDxfId="0" dataCellStyle="Percent" totalsRowCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{837B4DEA-431B-8140-90EC-AF1426BB3C6B}" name="Grade you got" totalsRowLabel=" 90.00 " totalsRowDxfId="0" dataCellStyle="Comma" totalsRowCellStyle="Comma"/>
     <tableColumn id="3" xr3:uid="{AF7FE643-1643-E748-AC40-8840F62189AD}" name="Points" totalsRowLabel="10"/>
     <tableColumn id="4" xr3:uid="{F50225EC-AD5E-3149-82B1-A97F692CCCFE}" name="Points Earned" totalsRowFunction="custom">
       <calculatedColumnFormula>IF(OR(F3="",G3=""),"",F3/100*G3)</calculatedColumnFormula>
@@ -652,10 +962,7 @@
     <tableColumn id="1" xr3:uid="{10981371-B7C9-3E42-B016-B99B8D9809D7}" name="Assignment Name"/>
     <tableColumn id="2" xr3:uid="{32334DF6-052D-E942-BC3A-0F6C0671E85C}" name="Grade you got" totalsRowLabel="9000%" totalsRowDxfId="2" dataCellStyle="Percent" totalsRowCellStyle="Percent"/>
     <tableColumn id="3" xr3:uid="{62EB5C69-F8F5-4948-9EB3-57D0F87BDFC3}" name="Points" totalsRowLabel="10"/>
-    <tableColumn id="4" xr3:uid="{2C672AD3-1CA4-CB42-86BD-2D3F01414F43}" name="Points Earned" totalsRowFunction="custom">
-      <calculatedColumnFormula>IF(OR(F3="",G3=""),"",F3/100*G3)</calculatedColumnFormula>
-      <totalsRowFormula>IF(OR(F4="",G4=""),"",F4/100*G4)</totalsRowFormula>
-    </tableColumn>
+    <tableColumn id="4" xr3:uid="{2C672AD3-1CA4-CB42-86BD-2D3F01414F43}" name="Points Earned" totalsRowLabel="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -665,15 +972,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{E1AAE215-0FDF-3A46-934E-F8714FC06EC3}" name="Table12192225" displayName="Table12192225" ref="K2:M3" totalsRowShown="0">
   <autoFilter ref="K2:M3" xr:uid="{E1AAE215-0FDF-3A46-934E-F8714FC06EC3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1360343D-D793-8A4C-800D-172BE7BD955B}" name="Formative" dataCellStyle="Percent">
-      <calculatedColumnFormula>IFERROR(AVERAGE(C4:C10),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{FE402943-F37D-0045-A8A6-79829FCD3761}" name="Summative" dataCellStyle="Percent">
-      <calculatedColumnFormula>SUM(H:H)/SUM(G:G)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{71864CE1-1D2D-2840-8ACA-92DB42D33956}" name="Total">
-      <calculatedColumnFormula>0.6*L3+0.4*K3</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" xr3:uid="{1360343D-D793-8A4C-800D-172BE7BD955B}" name="Formative" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{FE402943-F37D-0045-A8A6-79829FCD3761}" name="Summative" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{71864CE1-1D2D-2840-8ACA-92DB42D33956}" name="Total"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -711,7 +1012,7 @@
   <autoFilter ref="K2:M3" xr:uid="{F327A9B8-E140-E14B-9203-91D32062422D}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{2638040B-E16A-A042-97CC-F101BB042EE0}" name="Formative" dataCellStyle="Percent">
-      <calculatedColumnFormula>IFERROR(AVERAGE(C4:C10),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IFERROR(AVERAGE(C:C),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{6B45BC5A-39CE-1945-8FDA-958C20292574}" name="Summative" dataCellStyle="Percent">
       <calculatedColumnFormula>SUM(H:H)/SUM(G:G)</calculatedColumnFormula>
@@ -1209,7 +1510,903 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DD8245-437E-7F45-935D-3F9A175781CC}">
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2">
+        <v>50</v>
+      </c>
+      <c r="D3" t="str">
+        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
+        <v>E</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
+      </c>
+      <c r="D4" t="str">
+        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
+        <v>A</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
+      </c>
+      <c r="D5" t="str">
+        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
+        <v>A</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5">
+        <v>100</v>
+      </c>
+      <c r="D6" t="str">
+        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
+        <v>A</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <f>AVERAGE(C3:C6)</f>
+        <v>87.5</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8">
+        <f>AVERAGE(Table3[QP])</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="str">
+        <f>VLOOKUP(C8,grade_table!A2:C9,3,1)</f>
+        <v>B+</v>
+      </c>
+      <c r="E9" t="str">
+        <f>VLOOKUP(E8,Table1[[#All],[QP Low]:[QP High]],2,1)</f>
+        <v>B</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B71DA2-84C5-C840-B6D6-1FBCBF6A77FA}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0.75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1.25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1.75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="13">
+        <v>2</v>
+      </c>
+      <c r="D5" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2.25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="D6" s="13">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2.75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="13">
+        <v>3</v>
+      </c>
+      <c r="D7" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>3.25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D8" s="13">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3.75</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13">
+        <v>4</v>
+      </c>
+      <c r="D9" s="12">
+        <v>5</v>
+      </c>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="13"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F17" s="12"/>
+      <c r="H17" s="13"/>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F19" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA11DC51-0B5C-ED4A-8666-9C21FDB555B7}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:G46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="7" width="10.83203125" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="2:7" ht="19" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+    </row>
+    <row r="4" spans="2:7" ht="48" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="21"/>
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0.81</v>
+      </c>
+      <c r="E6" s="27">
+        <v>0.81</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="21"/>
+      <c r="C7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.87852127659574497</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0.87852127659574497</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="21"/>
+      <c r="C8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.851112765957447</v>
+      </c>
+      <c r="E8" s="28">
+        <v>0.851112765957447</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="16">
+        <v>9</v>
+      </c>
+      <c r="E10" s="16">
+        <v>9</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="16">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="E11" s="16">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="30">
+        <v>90</v>
+      </c>
+      <c r="E12" s="30">
+        <v>90</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="16">
+        <v>10</v>
+      </c>
+      <c r="E13" s="16">
+        <v>10</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="16">
+        <v>9</v>
+      </c>
+      <c r="E14" s="16">
+        <v>9</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="17">
+        <v>90</v>
+      </c>
+      <c r="E15" s="17">
+        <v>90</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="16">
+        <v>25</v>
+      </c>
+      <c r="E16" s="16">
+        <v>25</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="16">
+        <v>22.5</v>
+      </c>
+      <c r="E17" s="16">
+        <v>22.5</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="17">
+        <v>85</v>
+      </c>
+      <c r="E18" s="17">
+        <v>85</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="16">
+        <v>25</v>
+      </c>
+      <c r="E19" s="16">
+        <v>25</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="16">
+        <v>21.25</v>
+      </c>
+      <c r="E20" s="16">
+        <v>21.25</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="17">
+        <v>89</v>
+      </c>
+      <c r="E21" s="17">
+        <v>89</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21"/>
+      <c r="C22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="16">
+        <v>25</v>
+      </c>
+      <c r="E22" s="16">
+        <v>25</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="16">
+        <v>22.25</v>
+      </c>
+      <c r="E23" s="16">
+        <v>22.25</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="17">
+        <v>75</v>
+      </c>
+      <c r="E24" s="17">
+        <v>75</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="16">
+        <v>10</v>
+      </c>
+      <c r="E25" s="16">
+        <v>10</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="E26" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="21"/>
+      <c r="C30" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="E30" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="21"/>
+      <c r="C31" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="21"/>
+      <c r="C32" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="21"/>
+      <c r="C33" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="21"/>
+      <c r="C36" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="37" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="21"/>
+      <c r="C37" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="21"/>
+      <c r="C38" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="E38" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="39" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="21"/>
+      <c r="C39" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="E40" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="21"/>
+      <c r="C42" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="17">
+        <v>0.86</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0.86</v>
+      </c>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F318234D-5E7A-E449-8885-6F5D460B60FE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D8459D-B693-FA4B-BC17-8503C776BC25}">
   <dimension ref="B1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1274,20 +2471,16 @@
         <v>9</v>
       </c>
       <c r="H3">
-        <f>IF(OR(F3="",G3=""),"",F3/100*G3)</f>
-        <v>8.1000000000000016E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="K3" s="14">
-        <f>IFERROR(AVERAGE(C4:C10),"")</f>
         <v>0.81</v>
       </c>
       <c r="L3" s="14">
-        <f>SUM(H:H)/SUM(G:G)</f>
-        <v>0.87852127659574475</v>
+        <v>0.87852127659574497</v>
       </c>
       <c r="M3">
-        <f>0.6*L3+0.4*K3</f>
-        <v>0.85111276595744689</v>
+        <v>0.851112765957447</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
@@ -1295,14 +2488,13 @@
         <v>0.8</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>39</v>
-      </c>
-      <c r="H4">
-        <f>IF(OR(F4="",G4=""),"",F4/100*G4)</f>
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
@@ -1316,7 +2508,6 @@
         <v>25</v>
       </c>
       <c r="H5">
-        <f>IF(OR(F5="",G5=""),"",F5/100*G5)</f>
         <v>22.5</v>
       </c>
     </row>
@@ -1331,7 +2522,6 @@
         <v>25</v>
       </c>
       <c r="H6">
-        <f>IF(OR(F6="",G6=""),"",F6/100*G6)</f>
         <v>21.25</v>
       </c>
     </row>
@@ -1346,7 +2536,6 @@
         <v>25</v>
       </c>
       <c r="H7">
-        <f>IF(OR(F7="",G7=""),"",F7/100*G7)</f>
         <v>22.25</v>
       </c>
     </row>
@@ -1361,7 +2550,6 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <f>IF(OR(F8="",G8=""),"",F8/100*G8)</f>
         <v>7.5</v>
       </c>
     </row>
@@ -1392,6 +2580,46 @@
       <c r="F14" s="14"/>
     </row>
   </sheetData>
+  <scenarios current="0">
+    <scenario name="Q1 calculater summative" locked="1" count="18" user="Arnez, Paul" comment="Created by Arnez, Paul on 10/1/2026_x000a_Modified by Arnez, Paul on 10/1/2026">
+      <inputCells r="F3" val="0.9" numFmtId="9"/>
+      <inputCells r="G3" val="9"/>
+      <inputCells r="H3" val="0.081"/>
+      <inputCells r="F4" val="90"/>
+      <inputCells r="G4" val="10"/>
+      <inputCells r="H4" val="9"/>
+      <inputCells r="F5" val="90" numFmtId="9"/>
+      <inputCells r="G5" val="25"/>
+      <inputCells r="H5" val="22.5"/>
+      <inputCells r="F6" val="85" numFmtId="9"/>
+      <inputCells r="G6" val="25"/>
+      <inputCells r="H6" val="21.25"/>
+      <inputCells r="F7" val="89" numFmtId="9"/>
+      <inputCells r="G7" val="25"/>
+      <inputCells r="H7" val="22.25"/>
+      <inputCells r="F8" val="75" numFmtId="9"/>
+      <inputCells r="G8" val="10"/>
+      <inputCells r="H8" val="7.5"/>
+    </scenario>
+    <scenario name="Q1 calculater Formative" locked="1" count="16" user="Arnez, Paul" comment="Created by Arnez, Paul on 10/1/2026">
+      <inputCells r="B2" val="Assignment Name"/>
+      <inputCells r="C2" val="Grade you got"/>
+      <inputCells r="B3" val=""/>
+      <inputCells r="C3" val="0.9" numFmtId="9"/>
+      <inputCells r="B4" val=""/>
+      <inputCells r="C4" val="0.8" numFmtId="9"/>
+      <inputCells r="B5" val=""/>
+      <inputCells r="C5" val="0.7" numFmtId="9"/>
+      <inputCells r="B6" val=""/>
+      <inputCells r="C6" val="0.75" numFmtId="9"/>
+      <inputCells r="B7" val=""/>
+      <inputCells r="C7" val="0.85" numFmtId="9"/>
+      <inputCells r="B8" val=""/>
+      <inputCells r="C8" val="0.9" numFmtId="9"/>
+      <inputCells r="B9" val=""/>
+      <inputCells r="C9" val="0.86" numFmtId="9"/>
+    </scenario>
+  </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="3">
     <tablePart r:id="rId1"/>
@@ -1401,7 +2629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8893D56-74D6-3B4A-9560-7DFC6B0D5F3C}">
   <dimension ref="B1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1457,7 +2685,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C3" s="14">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="F3" s="14">
         <v>0.9</v>
@@ -1470,8 +2698,8 @@
         <v>8.1000000000000016E-2</v>
       </c>
       <c r="K3" s="14">
-        <f>IFERROR(AVERAGE(C4:C10),"")</f>
-        <v>0.81</v>
+        <f>IFERROR(AVERAGE(C:C),"")</f>
+        <v>0.84</v>
       </c>
       <c r="L3" s="14">
         <f>SUM(H:H)/SUM(G:G)</f>
@@ -1479,18 +2707,18 @@
       </c>
       <c r="M3">
         <f>0.6*L3+0.4*K3</f>
-        <v>0.85111276595744689</v>
+        <v>0.8631127659574469</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C4" s="14">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
       </c>
       <c r="H4">
         <f>IF(OR(F4="",G4=""),"",F4/100*G4)</f>
@@ -1499,7 +2727,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C5" s="14">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="F5" s="14">
         <v>90</v>
@@ -1514,7 +2742,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C6" s="14">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="F6" s="14">
         <v>85</v>
@@ -1529,7 +2757,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C7" s="14">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="F7" s="14">
         <v>89</v>
@@ -1544,7 +2772,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C8" s="14">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="F8" s="14">
         <v>75</v>
@@ -1559,7 +2787,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C9" s="14">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="F9" s="14"/>
     </row>
@@ -1581,7 +2809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54749A2A-6951-3347-8554-10255A7A2278}">
   <dimension ref="B1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1668,10 +2896,10 @@
         <v>0.8</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
       </c>
       <c r="H4">
         <f>IF(OR(F4="",G4=""),"",F4/100*G4)</f>
@@ -1754,7 +2982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C8AD03-BF1D-2B41-AD73-E1E11BA54CD3}">
   <dimension ref="B1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1762,7 +2990,7 @@
     <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="19.1640625" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="15" customWidth="1"/>
     <col min="8" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1774,7 +3002,6 @@
       <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="14"/>
       <c r="K1" t="s">
         <v>33</v>
       </c>
@@ -1789,7 +3016,7 @@
       <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
@@ -1812,7 +3039,7 @@
       <c r="C3" s="14">
         <v>0.9</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <v>0.9</v>
       </c>
       <c r="G3">
@@ -1839,11 +3066,11 @@
       <c r="C4" s="14">
         <v>0.8</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
       </c>
       <c r="H4">
         <f>IF(OR(F4="",G4=""),"",F4/100*G4)</f>
@@ -1854,7 +3081,7 @@
       <c r="C5" s="14">
         <v>0.7</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="15">
         <v>90</v>
       </c>
       <c r="G5">
@@ -1869,7 +3096,7 @@
       <c r="C6" s="14">
         <v>0.75</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <v>85</v>
       </c>
       <c r="G6">
@@ -1884,7 +3111,7 @@
       <c r="C7" s="14">
         <v>0.85</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <v>89</v>
       </c>
       <c r="G7">
@@ -1899,7 +3126,7 @@
       <c r="C8" s="14">
         <v>0.9</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <v>75</v>
       </c>
       <c r="G8">
@@ -1914,15 +3141,12 @@
       <c r="C9" s="14">
         <v>0.86</v>
       </c>
-      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C10" s="14"/>
-      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C11" s="14"/>
-      <c r="F11" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1934,7 +3158,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567DDD9A-1BC3-5F40-B3BE-E90636EA7EDA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A09646-542F-1E4B-816F-1E2EB10CABEC}">
   <dimension ref="A2:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2031,316 +3264,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DD8245-437E-7F45-935D-3F9A175781CC}">
-  <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2">
-        <v>50</v>
-      </c>
-      <c r="D3" t="str">
-        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
-        <v>E</v>
-      </c>
-      <c r="E3">
-        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-      <c r="D4" t="str">
-        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
-        <v>A</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2">
-        <v>100</v>
-      </c>
-      <c r="D5" t="str">
-        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
-        <v>A</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5">
-        <v>100</v>
-      </c>
-      <c r="D6" t="str">
-        <f>VLOOKUP(Table3[[#This Row],[Grade]],grade_table!$A$2:$C$9,3,1)</f>
-        <v>A</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(Table3[[#This Row],[Letter]],qp_table!A$3:B$10,2)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <f>AVERAGE(C3:C6)</f>
-        <v>87.5</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8">
-        <f>AVERAGE(Table3[QP])</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="str">
-        <f>VLOOKUP(C8,grade_table!A2:C9,3,1)</f>
-        <v>B+</v>
-      </c>
-      <c r="E9" t="str">
-        <f>VLOOKUP(E8,Table1[[#All],[QP Low]:[QP High]],2,1)</f>
-        <v>B</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B71DA2-84C5-C840-B6D6-1FBCBF6A77FA}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="12">
-        <v>0</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0.75</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="13">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1.25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="D4" s="13">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1.75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="13">
-        <v>2</v>
-      </c>
-      <c r="D5" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2.25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="D6" s="13">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2.75</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="13">
-        <v>3</v>
-      </c>
-      <c r="D7" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>3.25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D8" s="13">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>3.75</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13">
-        <v>4</v>
-      </c>
-      <c r="D9" s="12">
-        <v>5</v>
-      </c>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G10" s="13"/>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="6:8" x14ac:dyDescent="0.2">
-      <c r="F17" s="12"/>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="6:8" x14ac:dyDescent="0.2">
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="6:8" x14ac:dyDescent="0.2">
-      <c r="F19" s="12"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>